--- a/docs/solution-survey-template.xlsx
+++ b/docs/solution-survey-template.xlsx
@@ -213,22 +213,46 @@
     <row r="12">
       <c r="A12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">⑥ 선택지</t>
+          <t xml:space="preserve">⑥ [ISSU 분류] 표시</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">드롭다운이 없는 칸(역할 슬롯·시뮬레이터 옵션)은 「선택지」 시트에서 ID 를 찾아 적으세요.</t>
+          <t xml:space="preserve">설명에 [ISSU 분류] 가 붙은 칸은 **우리 내부 분류 체계**입니다 (4-Layer·역할 슬롯·급·시뮬레이터 매핑 등). 제품을 잘 아셔도 이 값은 모르는 게 정상이니 비워두시면 ISSU 가 채웁니다. 나머지 칸이 조사해 주실 부분입니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">⑦ 다 채우면</t>
+          <t xml:space="preserve">⑦ 평가영역 강도</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">「3_판정데이터」의 A01~A10 은 **이 제품이 해결해 주는 영역**입니다. 아는 만큼 0~3 으로 적어주시면 ISSU 가 검토합니다. 열 설명에 각 영역의 주요 우려가 적혀 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">⑧ 선택지</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">드롭다운이 없는 칸(역할 슬롯·시뮬레이터 옵션)은 「선택지」 시트에서 ID 를 찾아 적으세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">⑨ 다 채우면</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">파일 그대로 ISSU 에 보내주세요. 시스템 등록은 ISSU 가 합니다.</t>
         </is>
@@ -398,7 +422,7 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">아키텍처상 어느 층인가</t>
+          <t xml:space="preserve">[ISSU 분류] 아키텍처상 어느 층인가 — 모르면 비워두세요</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
@@ -408,7 +432,7 @@
       </c>
       <c r="D2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MZC 오퍼링·MSP 와 얼마나 맞물리나</t>
+          <t xml:space="preserve">[ISSU 분류] MZC 오퍼링·MSP 와 얼마나 맞물리나 — 모르면 비워두세요</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -428,22 +452,22 @@
       </c>
       <c r="H2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">모르면 비워두세요</t>
+          <t xml:space="preserve">[ISSU 분류] 모르면 비워두세요</t>
         </is>
       </c>
       <c r="I2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">모르면 비워두세요</t>
+          <t xml:space="preserve">[ISSU 분류] 모르면 비워두세요</t>
         </is>
       </c>
       <c r="J2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MZC 내부 담당자 이름. 없으면 비워두세요</t>
+          <t xml:space="preserve">[ISSU 분류] MZC 내부 담당자. 모르면 비워두세요</t>
         </is>
       </c>
       <c r="K2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">지금 팔 수 있는 상태인가</t>
+          <t xml:space="preserve">[ISSU 분류] 지금 팔 수 있는 상태인가 — 모르면 비워두세요</t>
         </is>
       </c>
       <c r="L2" t="inlineStr" s="2">
@@ -508,7 +532,7 @@
       </c>
       <c r="X2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">전략·마진 코멘트. ⚠ 고객에게 노출되지 않습니다</t>
+          <t xml:space="preserve">[ISSU 분류] 전략·마진 코멘트. ⚠ 고객에게 노출되지 않습니다</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3719,7 @@
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">🔒 고객 미노출. AI Tech 의견 등</t>
+          <t xml:space="preserve">[ISSU 분류] 🔒 고객 미노출. AI Tech 의견 등</t>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="2">
@@ -3735,7 +3759,7 @@
       </c>
       <c r="K2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">🔒 고객 미노출. 마진·딜사이즈 전략</t>
+          <t xml:space="preserve">[ISSU 분류] 🔒 고객 미노출. 마진·딜사이즈 전략</t>
         </is>
       </c>
     </row>
@@ -5275,62 +5299,62 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">「선택지」 시트의 슬롯 ID 를 적으세요. **없으면 추천 후보가 되지 않습니다**</t>
+          <t xml:space="preserve">[ISSU 분류] 「선택지」 시트의 슬롯 ID. **없으면 추천 후보가 되지 않습니다** — 모르면 비워두세요</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SI·MSP 와 얼마나 묶이나</t>
+          <t xml:space="preserve">[ISSU 분류] SI·MSP 와 얼마나 묶이나 — 모르면 비워두세요</t>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">기밀정보·고객정보·소스코드 유출</t>
+          <t xml:space="preserve">주요 우려: 기밀정보·고객정보·소스코드 유출</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">해외 저장·백업 잔존·국외 이전</t>
+          <t xml:space="preserve">주요 우려: 해외 저장·백업 잔존·국외 이전</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">개인·공용·퇴사자 계정 통제 실패</t>
+          <t xml:space="preserve">주요 우려: 개인·공용·퇴사자 계정 통제 실패</t>
         </is>
       </c>
       <c r="G2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">비인가 내부 데이터 접근</t>
+          <t xml:space="preserve">주요 우려: 비인가 내부 데이터 접근</t>
         </is>
       </c>
       <c r="H2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">사고 원인·사용자 추적 불가</t>
+          <t xml:space="preserve">주요 우려: 사고 원인·사용자 추적 불가</t>
         </is>
       </c>
       <c r="I2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">위험한 작업의 임의 실행</t>
+          <t xml:space="preserve">주요 우려: 위험한 작업의 임의 실행</t>
         </is>
       </c>
       <c r="J2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">오답의 고객응대·의사결정 활용</t>
+          <t xml:space="preserve">주요 우려: 오답의 고객응대·의사결정 활용</t>
         </is>
       </c>
       <c r="K2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">법적 분쟁·자동화 의사결정 문제</t>
+          <t xml:space="preserve">주요 우려: 법적 분쟁·자동화 의사결정 문제</t>
         </is>
       </c>
       <c r="L2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">저작권·라이선스·계약 위반</t>
+          <t xml:space="preserve">주요 우려: 저작권·라이선스·계약 위반</t>
         </is>
       </c>
       <c r="M2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">비용 증가·ROI 부족·벤더 종속</t>
+          <t xml:space="preserve">주요 우려: 비용 증가·ROI 부족·벤더 종속</t>
         </is>
       </c>
       <c r="N2" t="inlineStr" s="2">
@@ -7337,7 +7361,7 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">「선택지」 시트의 옵션 ID 를 쉼표로. 예) q1_3, q4_2</t>
+          <t xml:space="preserve">[ISSU 분류] 「선택지」 시트의 옵션 ID 를 쉼표로. 예) q1_3, q4_2 — 모르면 비워두세요</t>
         </is>
       </c>
     </row>

--- a/docs/solution-survey-template.xlsx
+++ b/docs/solution-survey-template.xlsx
@@ -194,7 +194,7 @@
       </c>
       <c r="B10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">전제 조건·부적합 신호·구간 단가는 **평문으로** 적어주세요. ISSU 가 시스템 형식으로 옮깁니다. 형식을 맞추려다 틀리는 것보다 낫습니다.</t>
+          <t xml:space="preserve">전제 조건·부적합 신호·구간 단가는 **평문으로** 적어주세요. ISV BU 가 시스템 형식으로 옮깁니다. 형식을 맞추려다 틀리는 것보다 낫습니다.</t>
         </is>
       </c>
     </row>
@@ -213,12 +213,12 @@
     <row r="12">
       <c r="A12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">⑥ [ISSU 분류] 표시</t>
+          <t xml:space="preserve">⑥ [ISV BU 분류] 표시</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">설명에 [ISSU 분류] 가 붙은 칸은 **우리 내부 분류 체계**입니다 (4-Layer·역할 슬롯·급·시뮬레이터 매핑 등). 제품을 잘 아셔도 이 값은 모르는 게 정상이니 비워두시면 ISSU 가 채웁니다. 나머지 칸이 조사해 주실 부분입니다.</t>
+          <t xml:space="preserve">설명에 [ISV BU 분류] 가 붙은 칸은 **우리 내부 분류 체계**입니다 (4-Layer·역할 슬롯·급·시뮬레이터 매핑 등). 제품을 잘 아셔도 이 값은 모르는 게 정상이니 비워두시면 ISV BU 가 채웁니다. 나머지 칸이 조사해 주실 부분입니다.</t>
         </is>
       </c>
     </row>
@@ -230,7 +230,7 @@
       </c>
       <c r="B13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">「3_판정데이터」의 A01~A10 은 **이 제품이 해결해 주는 영역**입니다. 아는 만큼 0~3 으로 적어주시면 ISSU 가 검토합니다. 열 설명에 각 영역의 주요 우려가 적혀 있습니다.</t>
+          <t xml:space="preserve">「3_판정데이터」의 A01~A10 은 **이 제품이 해결해 주는 영역**입니다. 아는 만큼 0~3 으로 적어주시면 ISV BU 가 검토합니다. 열 설명에 각 영역의 주요 우려가 적혀 있습니다.</t>
         </is>
       </c>
     </row>
@@ -254,7 +254,7 @@
       </c>
       <c r="B15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">파일 그대로 ISSU 에 보내주세요. 시스템 등록은 ISSU 가 합니다.</t>
+          <t xml:space="preserve">파일 그대로 ISV BU 에 보내주세요. 시스템 등록은 ISV BU 가 합니다.</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">[ISSU 분류] 아키텍처상 어느 층인가 — 모르면 비워두세요</t>
+          <t xml:space="preserve">[ISV BU 분류] 아키텍처상 어느 층인가 — 모르면 비워두세요</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
@@ -432,7 +432,7 @@
       </c>
       <c r="D2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">[ISSU 분류] MZC 오퍼링·MSP 와 얼마나 맞물리나 — 모르면 비워두세요</t>
+          <t xml:space="preserve">[ISV BU 분류] MZC 오퍼링·MSP 와 얼마나 맞물리나 — 모르면 비워두세요</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -452,22 +452,22 @@
       </c>
       <c r="H2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">[ISSU 분류] 모르면 비워두세요</t>
+          <t xml:space="preserve">[ISV BU 분류] 모르면 비워두세요</t>
         </is>
       </c>
       <c r="I2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">[ISSU 분류] 모르면 비워두세요</t>
+          <t xml:space="preserve">[ISV BU 분류] 모르면 비워두세요</t>
         </is>
       </c>
       <c r="J2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">[ISSU 분류] MZC 내부 담당자. 모르면 비워두세요</t>
+          <t xml:space="preserve">[ISV BU 분류] MZC 내부 담당자. 모르면 비워두세요</t>
         </is>
       </c>
       <c r="K2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">[ISSU 분류] 지금 팔 수 있는 상태인가 — 모르면 비워두세요</t>
+          <t xml:space="preserve">[ISV BU 분류] 지금 팔 수 있는 상태인가 — 모르면 비워두세요</t>
         </is>
       </c>
       <c r="L2" t="inlineStr" s="2">
@@ -532,7 +532,7 @@
       </c>
       <c r="X2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">[ISSU 분류] 전략·마진 코멘트. ⚠ 고객에게 노출되지 않습니다</t>
+          <t xml:space="preserve">[ISV BU 분류] 전략·마진 코멘트. ⚠ 고객에게 노출되지 않습니다</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">[ISSU 분류] 🔒 고객 미노출. AI Tech 의견 등</t>
+          <t xml:space="preserve">[ISV BU 분류] 🔒 고객 미노출. AI Tech 의견 등</t>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="2">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="K2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">[ISSU 분류] 🔒 고객 미노출. 마진·딜사이즈 전략</t>
+          <t xml:space="preserve">[ISV BU 분류] 🔒 고객 미노출. 마진·딜사이즈 전략</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">[ISSU 분류] 「선택지」 시트의 슬롯 ID. **없으면 추천 후보가 되지 않습니다** — 모르면 비워두세요</t>
+          <t xml:space="preserve">[ISV BU 분류] 「선택지」 시트의 슬롯 ID. **없으면 추천 후보가 되지 않습니다** — 모르면 비워두세요</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">[ISSU 분류] SI·MSP 와 얼마나 묶이나 — 모르면 비워두세요</t>
+          <t xml:space="preserve">[ISV BU 분류] SI·MSP 와 얼마나 묶이나 — 모르면 비워두세요</t>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="2">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">[ISSU 분류] 「선택지」 시트의 옵션 ID 를 쉼표로. 예) q1_3, q4_2 — 모르면 비워두세요</t>
+          <t xml:space="preserve">[ISV BU 분류] 「선택지」 시트의 옵션 ID 를 쉼표로. 예) q1_3, q4_2 — 모르면 비워두세요</t>
         </is>
       </c>
     </row>
